--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,110 +531,334 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,102 +531,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>250.01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.4812</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,102 +635,94 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>141.16</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1.3438</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,110 +739,1062 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.6173</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1785459609</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.510214</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>1785459608</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>112.676056</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>281.690141</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,23 +947,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,23 +1051,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,23 +1155,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,18 +1259,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,23 +1363,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1395,27 +1395,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1440,17 +1440,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,102 +1467,94 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>250.01</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1.4812</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,102 +1571,94 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>141.16</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1.3438</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,110 +1675,542 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,18 +643,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,23 +851,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -979,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1024,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,23 +1059,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1128,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1138,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,23 +1163,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1232,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,23 +1267,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1336,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,18 +1371,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1440,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1450,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,18 +1475,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1544,7 +1552,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1554,7 +1562,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1571,18 +1579,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1648,7 +1656,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1658,7 +1666,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1675,18 +1683,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1762,7 +1770,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1779,23 +1787,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1811,27 +1819,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1856,17 +1864,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1883,92 +1891,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>250.01</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1.4812</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459478</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>383.136691</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,7 +1995,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>250.01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785441463</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>519.501299</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,110 +2107,222 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,84 +539,76 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>18.41999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.5038</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19614758</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,31 +635,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -883,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,28 +971,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -987,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1032,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,23 +1075,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1136,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1179,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1211,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1256,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1283,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1299,27 +1315,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1360,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,23 +1387,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1448,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,23 +1491,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1552,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,23 +1595,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1656,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1666,7 +1682,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,18 +1699,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1760,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1770,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,18 +1803,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1864,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1874,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,23 +1907,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1923,27 +1939,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1968,17 +1984,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,102 +2011,94 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>250.01</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1.4812</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,102 +2115,94 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>141.16</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1.3438</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>L19605615</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,110 +2219,438 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,36 +531,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -578,7 +586,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,27 +643,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -663,11 +667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -675,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,27 +747,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -775,34 +771,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -832,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -867,19 +859,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -887,11 +875,7 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -914,7 +898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +928,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +938,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,31 +955,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1003,27 +995,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1048,17 +1040,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1075,31 +1067,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1107,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,31 +1179,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1211,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1315,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1360,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1387,23 +1395,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,28 +1499,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1523,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,28 +1603,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1627,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,23 +1707,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1776,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,23 +1811,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1880,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1890,7 +1898,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,23 +1915,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1984,7 +1992,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,18 +2019,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2098,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,18 +2123,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2192,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2210,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,23 +2227,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2251,27 +2259,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2304,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,67 +2331,59 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,39 +2435,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2475,27 +2467,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2512,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,110 +2539,438 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,15 +643,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>1</t>
@@ -659,7 +663,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,7 +671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -763,7 +771,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -779,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,54 +971,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1194,29 +1194,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1291,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1323,27 +1331,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1376,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,18 +1403,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,28 +1507,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1531,27 +1539,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1584,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,23 +1611,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1680,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,28 +1715,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1739,27 +1747,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1792,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,23 +1819,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1888,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,23 +1923,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,23 +2027,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2096,7 +2104,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2106,7 +2114,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,18 +2131,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,18 +2235,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2304,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,18 +2339,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2408,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2418,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2435,18 +2443,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2522,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2539,23 +2547,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2571,27 +2579,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2616,17 +2624,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,54 +2651,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>133.14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>Mushuc Runa</t>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459478</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>383.136691</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,7 +2755,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2770,17 +2770,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>250.01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785441463</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>519.501299</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2867,110 +2867,222 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -683,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -771,12 +755,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -787,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,28 +843,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -891,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,28 +947,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -995,27 +979,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1024,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1051,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>15.83</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.3738</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1107,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,39 +1155,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1219,27 +1187,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1232,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,67 +1259,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1336,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,28 +1363,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1435,27 +1395,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1440,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,28 +1467,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1539,27 +1499,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1544,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,28 +1571,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1643,27 +1603,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1648,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1675,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1747,27 +1707,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1752,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1779,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1851,27 +1811,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1856,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,31 +1883,39 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1955,27 +1923,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +1968,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,31 +1995,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2059,27 +2035,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2104,17 +2080,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,28 +2107,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2163,27 +2139,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2184,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,28 +2211,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2267,27 +2243,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2312,17 +2288,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,28 +2315,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2371,27 +2347,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2392,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,31 +2419,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2475,27 +2459,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2504,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,31 +2531,39 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2579,27 +2571,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,17 +2616,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,31 +2643,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2683,27 +2683,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,67 +2755,59 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2840,17 +2832,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2867,39 +2859,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2907,27 +2891,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2952,17 +2936,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,110 +2963,1478 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.44982</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1785459886</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>0.6426</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>463.04</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1785459772</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>712.369231</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1785459616</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>22.555874</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1785459612</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>45.977011</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0.6173</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1785459609</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1.510214</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1785459608</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>112.676056</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>281.690141</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,31 +531,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,23 +651,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -667,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,23 +755,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -763,7 +783,11 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -786,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -854,12 +878,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -920,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -930,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,12 +982,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1024,7 +1048,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1058,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1075,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1107,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1152,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,7 +1179,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1166,17 +1190,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1202,7 +1226,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1232,7 +1256,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1242,7 +1266,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1259,7 +1283,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1270,17 +1294,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1306,7 +1330,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1336,7 +1360,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1346,7 +1370,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1363,7 +1387,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1374,17 +1398,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1410,7 +1434,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1440,7 +1464,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1450,7 +1474,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1467,7 +1491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1478,12 +1502,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1544,7 +1568,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1554,7 +1578,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1571,7 +1595,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1648,7 +1672,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1675,18 +1699,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1696,7 +1720,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1722,7 +1746,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1752,7 +1776,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1762,7 +1786,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1779,18 +1803,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1856,7 +1880,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1866,7 +1890,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1883,39 +1907,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1938,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1968,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1978,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,39 +2011,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2035,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,28 +2115,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2139,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,31 +2219,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2243,27 +2259,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2288,17 +2304,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2315,36 +2331,44 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -2362,7 +2386,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2392,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2402,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,27 +2443,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2447,11 +2467,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2459,27 +2475,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2504,17 +2520,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,27 +2547,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2559,34 +2571,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2634,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2643,7 +2651,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2651,19 +2659,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2671,11 +2675,7 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,31 +2755,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2787,27 +2795,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2832,17 +2840,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,31 +2867,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2891,27 +2907,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2936,17 +2952,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,31 +2979,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2995,27 +3019,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3040,17 +3064,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,28 +3091,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3099,27 +3123,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3144,17 +3168,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,23 +3195,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3248,7 +3272,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3258,7 +3282,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3275,28 +3299,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3307,27 +3331,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3352,17 +3376,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3379,28 +3403,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3411,27 +3435,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3456,17 +3480,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3483,23 +3507,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3560,7 +3584,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3570,7 +3594,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3587,23 +3611,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3664,7 +3688,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3674,7 +3698,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3691,23 +3715,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3768,7 +3792,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3778,7 +3802,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3795,18 +3819,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3872,7 +3896,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3882,7 +3906,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3899,18 +3923,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3976,7 +4000,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3986,7 +4010,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4003,23 +4027,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4035,27 +4059,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4080,17 +4104,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4107,67 +4131,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4192,17 +4208,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4219,39 +4235,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4259,27 +4267,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4304,17 +4312,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4331,110 +4339,438 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,52 +546,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,31 +867,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -899,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -992,7 +1000,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1018,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1075,28 +1083,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1107,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1152,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,28 +1187,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1211,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1256,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1283,7 +1291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1304,7 +1312,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1330,7 +1338,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1387,7 +1395,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1398,17 +1406,17 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1434,7 +1442,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1464,7 +1472,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1474,7 +1482,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1491,7 +1499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1512,7 +1520,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1538,7 +1546,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1568,7 +1576,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1595,7 +1603,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1606,17 +1614,17 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1642,7 +1650,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,7 +1680,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1682,7 +1690,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,7 +1707,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1720,7 +1728,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1746,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1803,7 +1811,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1880,7 +1888,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1907,7 +1915,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1928,7 +1936,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1954,7 +1962,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2011,18 +2019,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2088,7 +2096,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2098,7 +2106,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,7 +2123,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2136,7 +2144,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2162,7 +2170,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2192,7 +2200,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2219,7 +2227,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2227,31 +2235,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,12 +2331,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2346,22 +2346,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2371,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,15 +2443,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2459,7 +2463,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2467,7 +2471,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2475,27 +2483,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2528,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,7 +2555,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2563,7 +2571,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2579,27 +2587,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,17 +2632,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,28 +2659,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2698,7 +2706,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2728,7 +2736,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2738,7 +2746,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,7 +2763,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2763,54 +2771,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2994,29 +2994,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,31 +3091,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3123,27 +3131,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3168,17 +3176,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,18 +3203,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3272,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3282,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3299,28 +3307,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3331,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3376,17 +3384,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3403,23 +3411,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3480,7 +3488,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3498,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,28 +3515,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3539,27 +3547,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3584,17 +3592,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3611,23 +3619,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3688,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3698,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3715,23 +3723,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3792,7 +3800,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3802,7 +3810,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3819,23 +3827,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3896,7 +3904,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3906,7 +3914,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3923,18 +3931,18 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4000,7 +4008,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4010,7 +4018,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4027,18 +4035,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4104,7 +4112,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4114,7 +4122,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4131,18 +4139,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4208,7 +4216,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4218,7 +4226,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4235,18 +4243,18 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4322,7 +4330,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4339,23 +4347,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4371,27 +4379,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4416,17 +4424,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4443,54 +4451,46 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>133.14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>Mushuc Runa</t>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459478</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>383.136691</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4555,7 +4555,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4570,17 +4570,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>250.01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4812</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785441463</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>519.501299</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4667,110 +4667,222 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador -1</t>
-        </is>
-      </c>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -586,7 +578,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -616,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,59 +643,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,52 +754,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,67 +851,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,31 +955,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1026,7 +1010,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1056,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1066,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,31 +1067,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1160,7 +1152,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1170,7 +1162,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,15 +1179,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1203,43 +1199,47 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1264,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,28 +1291,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1323,27 +1323,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,23 +1395,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1419,7 +1423,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1472,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,31 +1507,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1531,27 +1547,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1592,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,7 +1619,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1611,23 +1627,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1635,27 +1659,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1680,17 +1704,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,31 +1731,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1739,27 +1771,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1816,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,7 +1843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1822,17 +1854,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1858,7 +1890,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1888,7 +1920,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1898,7 +1930,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1915,7 +1947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1926,12 +1958,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1992,7 +2024,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2002,7 +2034,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2019,28 +2051,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2051,27 +2083,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2096,17 +2128,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2123,23 +2155,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2200,7 +2232,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2210,7 +2242,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2227,23 +2259,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2304,7 +2336,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2314,7 +2346,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2331,39 +2363,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2386,7 +2410,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2416,7 +2440,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2450,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,39 +2467,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2483,27 +2499,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2528,17 +2544,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2555,28 +2571,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2587,27 +2603,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2632,17 +2648,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2659,28 +2675,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2691,27 +2707,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2736,17 +2752,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2763,28 +2779,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2795,27 +2811,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2840,17 +2856,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2867,39 +2883,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2907,27 +2915,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2952,17 +2960,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +2987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2987,31 +2995,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3019,27 +3019,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3064,17 +3064,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3099,59 +3099,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,17 +3168,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,31 +3195,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3235,27 +3235,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,31 +3307,39 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3339,27 +3347,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3384,17 +3392,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,23 +3419,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3443,27 +3451,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3488,17 +3496,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,23 +3523,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3547,27 +3555,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3592,17 +3600,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,28 +3627,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3651,27 +3659,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3696,17 +3704,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,31 +3731,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3755,27 +3771,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3800,17 +3816,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,31 +3843,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3859,27 +3883,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3904,17 +3928,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3931,31 +3955,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3963,27 +3995,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4008,17 +4040,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4035,23 +4067,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4112,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4122,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4139,23 +4171,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4216,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4226,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4243,28 +4275,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4275,27 +4307,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4320,17 +4352,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4347,28 +4379,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4379,27 +4411,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4424,17 +4456,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4451,23 +4483,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4483,27 +4515,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4528,17 +4560,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4555,67 +4587,59 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4640,17 +4664,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4667,39 +4691,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4707,27 +4723,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4752,17 +4768,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4779,110 +4795,958 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1785459608</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>112.676056</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>281.690141</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -646,12 +646,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -667,27 +667,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +712,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,12 +739,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -779,27 +779,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -824,17 +824,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,7 +851,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -862,12 +862,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -883,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -963,19 +963,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -983,11 +979,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -995,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,39 +1059,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1122,7 +1106,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1152,7 +1136,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1162,7 +1146,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1179,7 +1163,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1187,19 +1171,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1207,11 +1187,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1234,7 +1210,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1240,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1250,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,31 +1267,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1323,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1368,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,39 +1379,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1450,7 +1426,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1480,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1522,52 +1498,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1592,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1619,12 +1595,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1634,52 +1610,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,12 +1707,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1746,52 +1722,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1816,17 +1792,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1843,28 +1819,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1875,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1920,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1947,23 +1923,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1971,7 +1951,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2024,7 +2008,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2034,7 +2018,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2051,23 +2035,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2075,7 +2063,11 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2098,7 +2090,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2128,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2138,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2155,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,23 +2155,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2187,27 +2187,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,31 +2259,39 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2291,27 +2299,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2336,17 +2344,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2363,7 +2371,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2374,12 +2382,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2440,7 +2448,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2450,7 +2458,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2467,7 +2475,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2478,12 +2486,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2544,7 +2552,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2554,7 +2562,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,28 +2579,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2603,27 +2611,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2648,17 +2656,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2675,7 +2683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2686,17 +2694,17 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2722,7 +2730,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2752,7 +2760,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2762,7 +2770,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2779,7 +2787,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2790,12 +2798,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2856,7 +2864,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2866,7 +2874,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2883,7 +2891,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2894,12 +2902,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2960,7 +2968,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2970,7 +2978,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2987,28 +2995,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3034,7 +3042,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3064,7 +3072,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3074,7 +3082,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3091,18 +3099,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3138,7 +3146,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3168,7 +3176,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3178,7 +3186,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3195,39 +3203,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,39 +3307,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3347,27 +3339,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3392,17 +3384,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3419,28 +3411,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3451,27 +3443,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3496,17 +3488,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3523,28 +3515,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3555,27 +3547,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3600,17 +3592,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3627,7 +3619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3638,17 +3630,17 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3659,27 +3651,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3704,17 +3696,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3731,7 +3723,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3746,22 +3738,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3771,27 +3763,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3816,17 +3808,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3843,12 +3835,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3858,12 +3850,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3873,32 +3865,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3928,7 +3920,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +3930,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,67 +3947,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4040,17 +4024,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4067,28 +4051,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4099,27 +4083,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4144,17 +4128,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,28 +4155,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4203,27 +4187,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4248,17 +4232,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,23 +4259,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4299,7 +4287,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4307,27 +4299,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4352,17 +4344,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4379,23 +4371,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4403,7 +4399,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4411,27 +4411,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4456,17 +4456,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4483,31 +4483,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4515,27 +4523,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4560,17 +4568,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4587,23 +4595,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4664,7 +4672,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4674,7 +4682,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4691,23 +4699,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4768,7 +4776,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4778,7 +4786,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4795,28 +4803,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4827,27 +4835,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4872,17 +4880,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4899,28 +4907,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4931,27 +4939,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4976,17 +4984,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5003,23 +5011,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5080,7 +5088,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5090,7 +5098,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5107,12 +5115,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -5123,7 +5131,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5184,7 +5192,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5211,23 +5219,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5288,7 +5296,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5298,7 +5306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5315,23 +5323,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5347,27 +5355,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5392,17 +5400,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5419,67 +5427,59 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,39 +5531,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5571,27 +5563,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5616,17 +5608,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5643,110 +5635,646 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V55"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
+          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -542,12 +542,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.94998</t>
+          <t>2.25205</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785625675</t>
+          <t>1785631027</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>33.830481</t>
+          <t>3.144223</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
+          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.03999</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -682,7 +690,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +720,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785623924</t>
+          <t>1785631010</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +730,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>31.579851</t>
+          <t>35.392405</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,7 +747,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
+          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -754,12 +762,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.01902</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785622155</t>
+          <t>1785630610</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3.30047</t>
+          <t>31.049505</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,23 +859,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
+          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.76998</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -898,7 +906,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -928,7 +936,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785622131</t>
+          <t>1785630479</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -938,7 +946,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>32.013441</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,23 +963,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
+          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>19.24054</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785618894</t>
+          <t>1785629993</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>8.595186</t>
+          <t>30.240534</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1067,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>18.93057</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1099,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1144,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785629981</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>29.811921</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,23 +1171,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>0.20642</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1195,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785629980</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>0.325071</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,27 +1275,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20.8767</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1295,11 +1299,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Tecnico U.</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1307,27 +1307,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785629947</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>32.876693</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,23 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>1.74447</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1456,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785629890</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>2.808</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,27 +1483,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>19.68316</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1511,11 +1507,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1523,27 +1515,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1560,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785629849</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>31.683155</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,27 +1587,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>22.72134</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1623,11 +1611,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1635,27 +1619,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1680,17 +1664,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785629842</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>36.647323</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,27 +1691,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.12077</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1735,11 +1715,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1747,27 +1723,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1768,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785629837</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>0.19479</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1795,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22.96368</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1851,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>36.96367</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,39 +1899,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21.21051</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1963,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2008,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>34.2105</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2035,67 +2003,59 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>21.09838</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2120,17 +2080,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785629804</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>34.029645</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,67 +2107,59 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>0.11216</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2232,17 +2184,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785629795</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>0.180903</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2259,67 +2211,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>22.7213</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2344,17 +2288,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785629790</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>36.721293</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2371,28 +2315,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>22.6013</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2403,27 +2347,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2448,17 +2392,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785629787</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>36.601296</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2475,28 +2419,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>20.65695</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2507,27 +2451,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2552,17 +2496,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785629635</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>33.656945</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2579,28 +2523,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.75999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2611,27 +2555,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2600,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>7.771412</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,28 +2627,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>22.01285</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2715,27 +2659,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2704,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>36.012843</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,28 +2731,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.31349</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2819,27 +2763,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2864,17 +2808,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785629531</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>26.908849</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2891,31 +2835,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>7.01336</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2923,27 +2875,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2968,17 +2920,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785629517</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>21.496889</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2995,28 +2947,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>18.47618</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3027,27 +2979,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3072,17 +3024,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785629509</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>30.476173</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3099,31 +3051,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>7.01963</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3131,27 +3091,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3176,17 +3136,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785629505</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>21.516107</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3203,28 +3163,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>14.42809</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3235,27 +3195,27 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3280,17 +3240,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785629494</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>23.848083</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3307,28 +3267,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>102.61</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3339,27 +3299,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3384,17 +3344,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785629314</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>172.816842</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3411,28 +3371,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3443,27 +3403,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3488,17 +3448,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3515,7 +3475,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3526,17 +3486,17 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3547,27 +3507,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3592,17 +3552,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3619,7 +3579,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3627,23 +3587,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3651,27 +3619,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3696,17 +3664,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,7 +3691,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3731,31 +3699,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3763,27 +3723,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3808,17 +3768,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3835,27 +3795,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3863,11 +3819,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3875,27 +3827,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3920,17 +3872,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3947,28 +3899,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3979,27 +3931,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4024,17 +3976,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4051,23 +4003,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4083,27 +4035,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4128,17 +4080,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4155,59 +4107,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4232,17 +4192,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4259,7 +4219,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4267,19 +4227,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4287,11 +4243,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4299,27 +4251,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4344,17 +4296,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4371,7 +4323,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4386,12 +4338,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4401,7 +4353,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4411,27 +4363,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4456,17 +4408,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4483,7 +4435,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4498,52 +4450,52 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4568,17 +4520,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,31 +4547,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4627,27 +4587,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4672,17 +4632,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,28 +4659,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4731,27 +4691,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4776,17 +4736,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4803,31 +4763,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4835,27 +4803,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4880,17 +4848,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4907,31 +4875,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4954,7 +4930,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4984,7 +4960,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4994,7 +4970,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5011,31 +4987,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5043,27 +5027,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5088,17 +5072,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5115,31 +5099,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5147,27 +5139,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5192,17 +5184,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5219,28 +5211,28 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5251,27 +5243,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5296,17 +5288,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5323,28 +5315,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5355,27 +5347,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5400,17 +5392,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5427,28 +5419,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5459,27 +5451,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5504,17 +5496,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5531,28 +5523,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5563,27 +5555,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5608,17 +5600,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5635,28 +5627,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5667,27 +5659,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5712,17 +5704,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5739,28 +5731,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5771,27 +5763,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5816,17 +5808,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5843,28 +5835,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5875,27 +5867,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5920,17 +5912,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5947,67 +5939,59 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6032,17 +6016,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6059,39 +6043,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6099,27 +6075,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6144,17 +6120,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6171,110 +6147,2974 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>15.67</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.5375</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19606829</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1785559105</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1785619800</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>29.153488</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>15.67</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.5375</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19606829</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1785559105</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1785619800</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>29.153488</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>173.57</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.5375</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19606829</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1785557644</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1785619800</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>322.92093</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>173.57</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.5375</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19606829</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1785557643</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1785619800</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>322.92093</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.4062</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19606829</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1785540081</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1785619800</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>5.76</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.3313</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1785524760</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>3.018868</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.5913</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Emelec vs Aucas</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19607503</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1785513340</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1785628800</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1.691332</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.6825</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1785513160</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1.465201</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>18.41999</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.5537</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1785497374</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>33.26409</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.3738</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1785497256</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>4.120401</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>15.65</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.3738</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1785497255</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>41.87291</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.5038</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19614758</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1785487800</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1785542400</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>7.543424</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1785460511</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>27.210884</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.3675</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1785460290</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>26.122449</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>0.44982</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1785459886</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>0.6426</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>463.04</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1785459772</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>712.369231</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1785459616</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>22.555874</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1785459612</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>45.977011</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>0.6173</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1785459609</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>1.510214</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1785459608</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>112.676056</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>281.690141</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="T82" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="U82" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="V82" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V82"/>
+  <dimension ref="A1:V85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
+          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -539,15 +539,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.25205</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785631027</t>
+          <t>1785643501</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3.144223</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
+          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785631010</t>
+          <t>1785643470</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>35.392405</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
+          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -762,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -777,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -787,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785630610</t>
+          <t>1785643468</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>31.049505</t>
+          <t>26.085603</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,23 +867,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
+          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2.25205</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -906,7 +914,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -936,7 +944,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785630479</t>
+          <t>1785631027</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -946,7 +954,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>3.144223</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,7 +971,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
+          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -971,15 +979,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.24054</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6362</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -987,7 +999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1010,7 +1026,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1040,7 +1056,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785629993</t>
+          <t>1785631010</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1050,7 +1066,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>30.240534</t>
+          <t>35.392405</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,23 +1083,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
+          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.93057</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1091,7 +1111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1114,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1144,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785629981</t>
+          <t>1785630610</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1154,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>29.811921</t>
+          <t>31.049505</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
+          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,12 +1206,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.20642</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1248,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785629980</t>
+          <t>1785630479</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1258,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.325071</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,7 +1299,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
+          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1286,12 +1310,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20.8767</t>
+          <t>19.24054</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785629947</t>
+          <t>1785629993</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1386,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>32.876693</t>
+          <t>30.240534</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,7 +1403,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
+          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1390,12 +1414,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.74447</t>
+          <t>18.93057</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1456,7 +1480,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785629890</t>
+          <t>1785629981</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1466,7 +1490,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.808</t>
+          <t>29.811921</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,7 +1507,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
+          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1494,12 +1518,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.68316</t>
+          <t>0.20642</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1560,7 +1584,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785629849</t>
+          <t>1785629980</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1570,7 +1594,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>31.683155</t>
+          <t>0.325071</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1587,7 +1611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
+          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1598,12 +1622,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22.72134</t>
+          <t>20.8767</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1664,7 +1688,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785629842</t>
+          <t>1785629947</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1674,7 +1698,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>36.647323</t>
+          <t>32.876693</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1691,7 +1715,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
+          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1702,12 +1726,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.12077</t>
+          <t>1.74447</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1768,7 +1792,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785629837</t>
+          <t>1785629890</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1778,7 +1802,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0.19479</t>
+          <t>2.808</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1795,7 +1819,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
+          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1806,7 +1830,7 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22.96368</t>
+          <t>19.68316</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1872,7 +1896,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629849</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1882,7 +1906,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>36.96367</t>
+          <t>31.683155</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
+          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1910,7 +1934,7 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21.21051</t>
+          <t>22.72134</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1976,7 +2000,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629842</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +2010,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>34.2105</t>
+          <t>36.647323</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
+          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2014,7 +2038,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21.09838</t>
+          <t>0.12077</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2080,7 +2104,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785629804</t>
+          <t>1785629837</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2090,7 +2114,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>34.029645</t>
+          <t>0.19479</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,7 +2131,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
+          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2118,12 +2142,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.11216</t>
+          <t>22.96368</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2184,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785629795</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2194,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.180903</t>
+          <t>36.96367</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,7 +2235,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
+          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2222,12 +2246,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22.7213</t>
+          <t>21.21051</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2288,7 +2312,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785629790</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2298,7 +2322,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36.721293</t>
+          <t>34.2105</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2315,7 +2339,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
+          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2326,12 +2350,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.6013</t>
+          <t>21.09838</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2392,7 +2416,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785629787</t>
+          <t>1785629804</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2402,7 +2426,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36.601296</t>
+          <t>34.029645</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,7 +2443,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
+          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2430,12 +2454,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.65695</t>
+          <t>0.11216</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2496,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785629635</t>
+          <t>1785629795</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2506,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>33.656945</t>
+          <t>0.180903</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,23 +2547,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
+          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.75999</t>
+          <t>22.7213</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2600,7 +2624,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629790</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2610,7 +2634,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>7.771412</t>
+          <t>36.721293</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2627,7 +2651,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
+          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2638,12 +2662,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.01285</t>
+          <t>22.6013</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2704,7 +2728,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629787</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2714,7 +2738,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36.012843</t>
+          <t>36.601296</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2731,7 +2755,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
+          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2742,12 +2766,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16.31349</t>
+          <t>20.65695</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2808,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785629531</t>
+          <t>1785629635</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2818,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>26.908849</t>
+          <t>33.656945</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2835,27 +2859,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
+          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.01336</t>
+          <t>4.75999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2863,11 +2883,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2890,7 +2906,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2920,7 +2936,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785629517</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2930,7 +2946,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>21.496889</t>
+          <t>7.771412</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2947,7 +2963,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
+          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2958,12 +2974,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18.47618</t>
+          <t>22.01285</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3024,7 +3040,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785629509</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3034,7 +3050,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>30.476173</t>
+          <t>36.012843</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3051,7 +3067,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
+          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3059,19 +3075,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.01963</t>
+          <t>16.31349</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3079,11 +3091,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3106,7 +3114,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3136,7 +3144,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785629505</t>
+          <t>1785629531</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3146,7 +3154,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>21.516107</t>
+          <t>26.908849</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3163,7 +3171,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
+          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3171,15 +3179,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>14.42809</t>
+          <t>7.01336</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3187,7 +3199,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3210,7 +3226,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3240,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785629494</t>
+          <t>1785629517</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3250,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>23.848083</t>
+          <t>21.496889</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3267,23 +3283,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
+          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>102.61</t>
+          <t>18.47618</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3344,7 +3360,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785629314</t>
+          <t>1785629509</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3354,7 +3370,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>172.816842</t>
+          <t>30.476173</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3371,23 +3387,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
+          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>24.94998</t>
+          <t>7.01963</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3395,7 +3415,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3418,7 +3442,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3448,7 +3472,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785625675</t>
+          <t>1785629505</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3458,7 +3482,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>33.830481</t>
+          <t>21.516107</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3475,23 +3499,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
+          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18.03999</t>
+          <t>14.42809</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3552,7 +3576,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785623924</t>
+          <t>1785629494</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3562,7 +3586,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>31.579851</t>
+          <t>23.848083</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3579,7 +3603,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
+          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3587,19 +3611,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1.01902</t>
+          <t>102.61</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3607,11 +3627,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3634,7 +3650,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3664,7 +3680,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785622155</t>
+          <t>1785629314</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3674,7 +3690,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3.30047</t>
+          <t>172.816842</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3691,7 +3707,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3702,12 +3718,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>23.76998</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3768,7 +3784,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785622131</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3778,7 +3794,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>32.013441</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3795,7 +3811,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3806,7 +3822,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3872,7 +3888,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785618894</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3882,7 +3898,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>8.595186</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3899,59 +3915,67 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3976,17 +4000,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4003,7 +4027,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4014,12 +4038,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4035,27 +4059,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4080,17 +4104,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4107,27 +4131,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4135,11 +4155,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Tecnico U.</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4147,27 +4163,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4192,17 +4208,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4219,28 +4235,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4266,7 +4282,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4296,7 +4312,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4306,7 +4322,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4323,7 +4339,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4331,19 +4347,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4351,11 +4363,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4378,7 +4386,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4408,7 +4416,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4418,7 +4426,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4435,12 +4443,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4450,12 +4458,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4465,7 +4473,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4490,7 +4498,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4520,7 +4528,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4530,7 +4538,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4547,7 +4555,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4555,19 +4563,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4575,11 +4579,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4667,23 +4667,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4691,27 +4699,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4736,17 +4744,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4763,12 +4771,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4778,22 +4786,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4818,7 +4826,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4848,7 +4856,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4858,7 +4866,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4875,7 +4883,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4890,52 +4898,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4960,17 +4968,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4987,44 +4995,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>Manta FC vs Mushuc Runa</t>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5099,12 +5099,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5114,52 +5114,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5184,17 +5184,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5211,31 +5211,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5243,27 +5251,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5288,17 +5296,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5315,7 +5323,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5323,23 +5331,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5347,27 +5363,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5392,17 +5408,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5419,23 +5435,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5443,7 +5463,11 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5466,7 +5490,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5496,7 +5520,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5506,7 +5530,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5523,7 +5547,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5534,12 +5558,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5600,7 +5624,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5610,7 +5634,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5627,7 +5651,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5638,12 +5662,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5704,7 +5728,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5714,7 +5738,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5731,28 +5755,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5763,27 +5787,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5808,17 +5832,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5835,7 +5859,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5846,17 +5870,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5882,7 +5906,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5912,7 +5936,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5922,7 +5946,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5939,7 +5963,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5950,17 +5974,17 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5986,7 +6010,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -6016,7 +6040,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -6026,7 +6050,7 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6043,7 +6067,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6054,17 +6078,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6090,7 +6114,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -6120,7 +6144,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6130,7 +6154,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6147,7 +6171,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6158,12 +6182,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6224,7 +6248,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6234,7 +6258,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6251,7 +6275,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6328,7 +6352,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6355,18 +6379,18 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6376,7 +6400,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6402,7 +6426,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6432,7 +6456,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6442,7 +6466,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6459,18 +6483,18 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6536,7 +6560,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6546,7 +6570,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6563,39 +6587,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6618,7 +6634,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6648,7 +6664,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6658,7 +6674,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6675,39 +6691,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6715,27 +6723,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6760,17 +6768,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6787,28 +6795,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6819,27 +6827,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6864,17 +6872,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6891,31 +6899,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6923,27 +6939,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6968,17 +6984,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -6995,36 +7011,44 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -7042,7 +7066,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7072,7 +7096,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7082,7 +7106,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7099,27 +7123,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7127,11 +7147,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7139,27 +7155,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7184,17 +7200,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7211,27 +7227,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7239,34 +7251,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -7296,7 +7304,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7306,7 +7314,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7323,7 +7331,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7331,19 +7339,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7351,11 +7355,7 @@
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7435,31 +7435,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7467,27 +7475,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7512,17 +7520,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7539,31 +7547,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7571,27 +7587,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7616,17 +7632,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7643,31 +7659,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7675,27 +7699,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7720,17 +7744,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7747,28 +7771,28 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -7779,27 +7803,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7824,17 +7848,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7851,23 +7875,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7928,7 +7952,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7938,7 +7962,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7955,28 +7979,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7987,27 +8011,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8032,17 +8056,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8059,28 +8083,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8091,27 +8115,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8136,17 +8160,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8163,23 +8187,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -8240,7 +8264,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8250,7 +8274,7 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8267,23 +8291,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8344,7 +8368,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8354,7 +8378,7 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8371,23 +8395,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8448,7 +8472,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8458,7 +8482,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8475,18 +8499,18 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -8552,7 +8576,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8562,7 +8586,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8579,18 +8603,18 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -8656,7 +8680,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8666,7 +8690,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8683,23 +8707,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8715,27 +8739,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8760,17 +8784,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8787,67 +8811,59 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8872,17 +8888,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8899,39 +8915,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8939,27 +8947,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -8984,17 +8992,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9011,110 +9019,438 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr">
+      <c r="T85" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="U85" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr">
+      <c r="V85" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V85"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
+          <t>0x214f483a273996aa10b912ab8fa07a65283ddd1ef8e14f95c317edc7d6c36ee2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785643501</t>
+          <t>1785660120</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>7.776892</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
+          <t>0x70ebb7c96f6896fbf14049a85100131a7e0367db64c5d8b3c6e7f9c4f0aecbd0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785643470</t>
+          <t>1785659777</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>11.314741</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
+          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19614996</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785643468</t>
+          <t>1785643501</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785702600</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>26.085603</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
+          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,15 +875,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.25205</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -891,7 +895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -899,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785631027</t>
+          <t>1785643470</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>3.144223</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +979,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
+          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,12 +994,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1001,7 +1009,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785631010</t>
+          <t>1785643468</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>35.392405</t>
+          <t>26.085603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,7 +1091,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
+          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1091,19 +1099,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>2.25205</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1111,11 +1115,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785630610</t>
+          <t>1785631027</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>31.049505</t>
+          <t>3.144223</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,7 +1195,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
+          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1203,15 +1203,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1219,7 +1223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1242,7 +1250,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1272,7 +1280,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785630479</t>
+          <t>1785631010</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1282,7 +1290,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>35.392405</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,23 +1307,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
+          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.24054</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6362</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1323,7 +1335,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1346,7 +1362,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1376,7 +1392,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785629993</t>
+          <t>1785630610</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1386,7 +1402,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>30.240534</t>
+          <t>31.049505</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,7 +1419,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
+          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1414,12 +1430,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.93057</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1480,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785629981</t>
+          <t>1785630479</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1490,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>29.811921</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
+          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1518,12 +1534,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.20642</t>
+          <t>19.24054</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1584,7 +1600,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785629980</t>
+          <t>1785629993</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1594,7 +1610,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.325071</t>
+          <t>30.240534</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,7 +1627,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
+          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1622,7 +1638,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20.8767</t>
+          <t>18.93057</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1688,7 +1704,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785629947</t>
+          <t>1785629981</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1698,7 +1714,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>32.876693</t>
+          <t>29.811921</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,7 +1731,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
+          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1726,12 +1742,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.74447</t>
+          <t>0.20642</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1792,7 +1808,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785629890</t>
+          <t>1785629980</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1818,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2.808</t>
+          <t>0.325071</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,7 +1835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
+          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1830,12 +1846,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.68316</t>
+          <t>20.8767</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1896,7 +1912,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785629849</t>
+          <t>1785629947</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1906,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>31.683155</t>
+          <t>32.876693</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,7 +1939,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
+          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1934,12 +1950,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22.72134</t>
+          <t>1.74447</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2000,7 +2016,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785629842</t>
+          <t>1785629890</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2010,7 +2026,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>36.647323</t>
+          <t>2.808</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,7 +2043,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
+          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2038,12 +2054,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.12077</t>
+          <t>19.68316</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2104,7 +2120,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785629837</t>
+          <t>1785629849</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2114,7 +2130,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0.19479</t>
+          <t>31.683155</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,7 +2147,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
+          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2142,12 +2158,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.96368</t>
+          <t>22.72134</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2208,7 +2224,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629842</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2218,7 +2234,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>36.96367</t>
+          <t>36.647323</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2251,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
+          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2246,7 +2262,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>21.21051</t>
+          <t>0.12077</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2312,7 +2328,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629837</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2338,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>34.2105</t>
+          <t>0.19479</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,7 +2355,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
+          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2350,12 +2366,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>21.09838</t>
+          <t>22.96368</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2416,7 +2432,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785629804</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2426,7 +2442,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>34.029645</t>
+          <t>36.96367</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,7 +2459,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
+          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2454,7 +2470,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.11216</t>
+          <t>21.21051</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2520,7 +2536,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785629795</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2530,7 +2546,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.180903</t>
+          <t>34.2105</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,7 +2563,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
+          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2558,12 +2574,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22.7213</t>
+          <t>21.09838</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2624,7 +2640,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785629790</t>
+          <t>1785629804</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2634,7 +2650,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>36.721293</t>
+          <t>34.029645</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,7 +2667,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
+          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2662,12 +2678,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22.6013</t>
+          <t>0.11216</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2728,7 +2744,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785629787</t>
+          <t>1785629795</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2738,7 +2754,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36.601296</t>
+          <t>0.180903</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,7 +2771,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
+          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2766,12 +2782,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.65695</t>
+          <t>22.7213</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2832,7 +2848,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785629635</t>
+          <t>1785629790</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2842,7 +2858,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>33.656945</t>
+          <t>36.721293</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,23 +2875,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
+          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.75999</t>
+          <t>22.6013</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2936,7 +2952,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629787</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2946,7 +2962,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7.771412</t>
+          <t>36.601296</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,7 +2979,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
+          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2974,12 +2990,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22.01285</t>
+          <t>20.65695</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3040,7 +3056,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629635</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3050,7 +3066,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.012843</t>
+          <t>33.656945</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3067,23 +3083,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
+          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16.31349</t>
+          <t>4.75999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3144,7 +3160,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785629531</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3154,7 +3170,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>26.908849</t>
+          <t>7.771412</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,7 +3187,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
+          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3179,19 +3195,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.01336</t>
+          <t>22.01285</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3199,11 +3211,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3226,7 +3234,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3256,7 +3264,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785629517</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3266,7 +3274,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>21.496889</t>
+          <t>36.012843</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,7 +3291,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
+          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3294,7 +3302,7 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18.47618</t>
+          <t>16.31349</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3360,7 +3368,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785629509</t>
+          <t>1785629531</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3370,7 +3378,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>30.476173</t>
+          <t>26.908849</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,7 +3395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
+          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3402,7 +3410,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.01963</t>
+          <t>7.01336</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3472,7 +3480,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785629505</t>
+          <t>1785629517</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3482,7 +3490,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21.516107</t>
+          <t>21.496889</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3499,7 +3507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
+          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3510,12 +3518,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14.42809</t>
+          <t>18.47618</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3576,7 +3584,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785629494</t>
+          <t>1785629509</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3586,7 +3594,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>23.848083</t>
+          <t>30.476173</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3603,23 +3611,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
+          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>102.61</t>
+          <t>7.01963</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3627,7 +3639,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3650,7 +3666,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3680,7 +3696,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785629314</t>
+          <t>1785629505</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3690,7 +3706,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>172.816842</t>
+          <t>21.516107</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3707,23 +3723,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
+          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>24.94998</t>
+          <t>14.42809</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3754,7 +3770,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3784,7 +3800,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785625675</t>
+          <t>1785629494</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3794,7 +3810,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>33.830481</t>
+          <t>23.848083</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3811,7 +3827,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
+          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3822,12 +3838,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18.03999</t>
+          <t>102.61</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3888,7 +3904,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785623924</t>
+          <t>1785629314</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3898,7 +3914,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>31.579851</t>
+          <t>172.816842</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3915,7 +3931,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3923,19 +3939,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.01902</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3943,11 +3955,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3970,7 +3978,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4000,7 +4008,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785622155</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4010,7 +4018,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>3.30047</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4027,7 +4035,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4038,12 +4046,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23.76998</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4074,7 +4082,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4104,7 +4112,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785622131</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4114,7 +4122,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>32.013441</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4131,7 +4139,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4139,15 +4147,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4155,7 +4167,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4178,7 +4194,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4208,7 +4224,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785618894</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4218,7 +4234,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8.595186</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4235,28 +4251,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4267,27 +4283,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4312,17 +4328,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4339,7 +4355,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4350,12 +4366,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4371,27 +4387,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4416,17 +4432,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4443,62 +4459,54 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Tecnico U.</t>
-        </is>
-      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4528,7 +4536,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4538,7 +4546,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4555,7 +4563,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4566,12 +4574,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4632,7 +4640,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4642,7 +4650,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4659,12 +4667,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4674,12 +4682,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4689,7 +4697,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4714,7 +4722,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4744,7 +4752,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4754,7 +4762,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4771,7 +4779,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4779,19 +4787,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4799,11 +4803,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4883,7 +4883,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4995,7 +4995,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5003,23 +5003,31 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5027,27 +5035,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5072,17 +5080,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5099,12 +5107,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5114,22 +5122,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador -1</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5154,7 +5162,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5184,7 +5192,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5211,7 +5219,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5219,36 +5227,28 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Under/Over (5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>Manta FC vs Mushuc Runa</t>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5323,12 +5323,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5338,52 +5338,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5408,17 +5408,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5435,12 +5435,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5547,7 +5547,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5555,23 +5555,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5579,27 +5587,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5624,17 +5632,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5651,31 +5659,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5683,27 +5699,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5728,17 +5744,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5755,28 +5771,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5787,27 +5803,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5832,17 +5848,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5859,7 +5875,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5870,17 +5886,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5906,7 +5922,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5936,7 +5952,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5946,7 +5962,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5963,28 +5979,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5995,27 +6011,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6040,17 +6056,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6067,7 +6083,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6078,12 +6094,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6144,7 +6160,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6154,7 +6170,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6171,7 +6187,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6182,12 +6198,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6248,7 +6264,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6258,7 +6274,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6275,7 +6291,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6286,12 +6302,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6352,7 +6368,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6362,7 +6378,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6379,7 +6395,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6390,12 +6406,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6456,7 +6472,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6466,7 +6482,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6483,7 +6499,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6504,7 +6520,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6530,7 +6546,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6560,7 +6576,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6587,7 +6603,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6608,7 +6624,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6634,7 +6650,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6664,7 +6680,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6691,18 +6707,18 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6712,7 +6728,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6738,7 +6754,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6768,7 +6784,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6778,7 +6794,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6795,18 +6811,18 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6816,7 +6832,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6842,7 +6858,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6872,7 +6888,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6882,7 +6898,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6899,7 +6915,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6907,31 +6923,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6954,7 +6962,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6984,7 +6992,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6994,7 +7002,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7011,39 +7019,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7051,27 +7051,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -7096,17 +7096,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7123,31 +7123,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7155,27 +7163,27 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -7200,17 +7208,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7227,15 +7235,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>1</t>
@@ -7243,7 +7255,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7251,7 +7263,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7304,7 +7320,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7314,7 +7330,7 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7331,28 +7347,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7363,27 +7379,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7408,17 +7424,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7435,27 +7451,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7463,34 +7475,30 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7520,7 +7528,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7530,7 +7538,7 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7547,7 +7555,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7555,54 +7563,46 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Libertad FC vs Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Orense Sporting Club</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7659,7 +7659,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7674,29 +7674,29 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -7714,7 +7714,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7771,31 +7771,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7803,27 +7811,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7848,17 +7856,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7875,31 +7883,39 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7907,27 +7923,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7952,17 +7968,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7979,28 +7995,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8011,27 +8027,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8056,17 +8072,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8083,28 +8099,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8115,27 +8131,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8160,17 +8176,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8187,28 +8203,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8219,27 +8235,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8264,17 +8280,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8291,28 +8307,28 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -8323,27 +8339,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8368,17 +8384,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8395,23 +8411,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -8472,7 +8488,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8482,7 +8498,7 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8499,23 +8515,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8576,7 +8592,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8586,7 +8602,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8603,23 +8619,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8680,7 +8696,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8690,7 +8706,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8707,18 +8723,18 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -8784,7 +8800,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8794,7 +8810,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8811,18 +8827,18 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8888,7 +8904,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8898,7 +8914,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8915,18 +8931,18 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8992,7 +9008,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459599</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -9002,7 +9018,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>45.070423</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9019,23 +9035,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9051,27 +9067,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9096,17 +9112,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>56.338028</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9123,67 +9139,59 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9208,17 +9216,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459589</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>22.535211</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9235,54 +9243,46 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>133.14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3475</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>Manta FC</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Manta FC vs Mushuc Runa</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
       <c r="K84" t="inlineStr">
         <is>
           <t>Mushuc Runa</t>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459478</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>383.136691</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9347,110 +9347,334 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr">
+      <c r="T87" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="U87" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr">
+      <c r="V87" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V87"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x214f483a273996aa10b912ab8fa07a65283ddd1ef8e14f95c317edc7d6c36ee2</t>
+          <t>0x8d2c872c09665cf9cf57507cd03dbbbaf226430f2b1442f9c0bb35deb32aa9ff</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.00062</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.3137</t>
+          <t>1.115</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785660120</t>
+          <t>1785681442</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7.776892</t>
+          <t>8.701043</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x70ebb7c96f6896fbf14049a85100131a7e0367db64c5d8b3c6e7f9c4f0aecbd0</t>
+          <t>0x6df2851dc28953254a2c8d565a7c08bfd0aaec8318f215c23034e37e288e72aa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,12 +658,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.3137</t>
+          <t>1.1162</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785659777</t>
+          <t>1785681442</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>11.314741</t>
+          <t>34.408602</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
+          <t>0x5754a527c5d40772803bfe08111607b869805453b6d724e4bed89cc5247bd2ad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +840,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785643501</t>
+          <t>1785681235</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>35.555556</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
+          <t>0x1655d0bff2fd6ee42ddf227545e1a447e622f1ae7851bd36a654f498c9012b54</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,19 +875,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -895,11 +891,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -907,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785643470</t>
+          <t>1785681139</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>2.739726</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,12 +971,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
+          <t>0x7118126433717b97d7c36bce57f6385f22f7e374269ac7ca377698d845607115</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -994,12 +986,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1009,7 +1001,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1019,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
+          <t>0xf87a3f407757b2ab8e98e67ca4abde0801cbe039cf02f0e2970781f2ca6d2e06</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19614996</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785643468</t>
+          <t>1785679495</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785702600</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>26.085603</t>
+          <t>13.157882</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,31 +1083,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
+          <t>0x4a6e59d1e415c1dc3913e9219fe2de6baa033f6752aea7f413784c5603109421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.25205</t>
+          <t>100.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Independiente del Valle -1.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xd1235982bd1809325631bb681de4216922f18a31740b3db578a0a014c1041b71</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785631027</t>
+          <t>1785678266</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3.144223</t>
+          <t>197.931034</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1195,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
+          <t>0x214f483a273996aa10b912ab8fa07a65283ddd1ef8e14f95c317edc7d6c36ee2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785631010</t>
+          <t>1785660120</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>35.392405</t>
+          <t>7.776892</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
+          <t>0x70ebb7c96f6896fbf14049a85100131a7e0367db64c5d8b3c6e7f9c4f0aecbd0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1347,27 +1347,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785630610</t>
+          <t>1785659777</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>31.049505</t>
+          <t>11.314741</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,23 +1419,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
+          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1443,7 +1447,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1451,27 +1459,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1496,17 +1504,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785630479</t>
+          <t>1785643501</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1523,23 +1531,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
+          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.24054</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.6362</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1547,7 +1559,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1555,27 +1571,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1600,17 +1616,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785629993</t>
+          <t>1785643470</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>30.240534</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1627,23 +1643,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
+          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18.93057</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1651,7 +1671,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Club Social Y Deportivo Macara</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1659,27 +1683,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1704,17 +1728,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785629981</t>
+          <t>1785643468</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>29.811921</t>
+          <t>26.085603</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1731,23 +1755,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
+          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.20642</t>
+          <t>2.25205</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1778,7 +1802,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1808,7 +1832,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785629980</t>
+          <t>1785631027</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1818,7 +1842,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0.325071</t>
+          <t>3.144223</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1835,7 +1859,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
+          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1843,15 +1867,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.8767</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1859,7 +1887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1882,7 +1914,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1912,7 +1944,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785629947</t>
+          <t>1785631010</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1922,7 +1954,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>32.876693</t>
+          <t>35.392405</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1939,23 +1971,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
+          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.74447</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1963,7 +1999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1986,7 +2026,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2016,7 +2056,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785629890</t>
+          <t>1785630610</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2026,7 +2066,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>2.808</t>
+          <t>31.049505</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2043,7 +2083,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
+          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2054,12 +2094,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.68316</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2120,7 +2160,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785629849</t>
+          <t>1785630479</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2130,7 +2170,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>31.683155</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2147,7 +2187,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
+          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,12 +2198,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22.72134</t>
+          <t>19.24054</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2224,7 +2264,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785629842</t>
+          <t>1785629993</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2234,7 +2274,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>36.647323</t>
+          <t>30.240534</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2251,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
+          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2262,12 +2302,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.12077</t>
+          <t>18.93057</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2328,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785629837</t>
+          <t>1785629981</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2338,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0.19479</t>
+          <t>29.811921</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2355,7 +2395,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
+          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2366,12 +2406,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22.96368</t>
+          <t>0.20642</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2432,7 +2472,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629980</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2442,7 +2482,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>36.96367</t>
+          <t>0.325071</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,7 +2499,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
+          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2470,12 +2510,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21.21051</t>
+          <t>20.8767</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2536,7 +2576,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785629947</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2546,7 +2586,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>34.2105</t>
+          <t>32.876693</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2563,7 +2603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
+          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2574,12 +2614,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>21.09838</t>
+          <t>1.74447</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2640,7 +2680,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785629804</t>
+          <t>1785629890</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2650,7 +2690,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>34.029645</t>
+          <t>2.808</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2667,7 +2707,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
+          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2678,12 +2718,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.11216</t>
+          <t>19.68316</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2744,7 +2784,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785629795</t>
+          <t>1785629849</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2754,7 +2794,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.180903</t>
+          <t>31.683155</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2771,7 +2811,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
+          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2782,12 +2822,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.7213</t>
+          <t>22.72134</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2848,7 +2888,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785629790</t>
+          <t>1785629842</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2858,7 +2898,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>36.721293</t>
+          <t>36.647323</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2875,7 +2915,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
+          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2886,12 +2926,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22.6013</t>
+          <t>0.12077</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2952,7 +2992,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785629787</t>
+          <t>1785629837</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2962,7 +3002,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>36.601296</t>
+          <t>0.19479</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2979,7 +3019,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
+          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2990,12 +3030,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20.65695</t>
+          <t>22.96368</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3056,7 +3096,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785629635</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3066,7 +3106,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>33.656945</t>
+          <t>36.96367</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3083,23 +3123,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
+          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4.75999</t>
+          <t>21.21051</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3160,7 +3200,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3170,7 +3210,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>7.771412</t>
+          <t>34.2105</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3187,7 +3227,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
+          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3198,12 +3238,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22.01285</t>
+          <t>21.09838</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3264,7 +3304,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629804</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3274,7 +3314,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>36.012843</t>
+          <t>34.029645</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3291,7 +3331,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
+          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3302,12 +3342,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>16.31349</t>
+          <t>0.11216</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3368,7 +3408,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785629531</t>
+          <t>1785629795</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3378,7 +3418,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>26.908849</t>
+          <t>0.180903</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3395,7 +3435,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
+          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3403,19 +3443,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.01336</t>
+          <t>22.7213</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3423,11 +3459,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3450,7 +3482,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3480,7 +3512,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785629517</t>
+          <t>1785629790</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3490,7 +3522,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>21.496889</t>
+          <t>36.721293</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3507,7 +3539,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
+          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3518,12 +3550,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18.47618</t>
+          <t>22.6013</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3584,7 +3616,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785629509</t>
+          <t>1785629787</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3594,7 +3626,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>30.476173</t>
+          <t>36.601296</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3611,7 +3643,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
+          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3619,19 +3651,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.01963</t>
+          <t>20.65695</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3639,11 +3667,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3666,7 +3690,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3696,7 +3720,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785629505</t>
+          <t>1785629635</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3706,7 +3730,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>21.516107</t>
+          <t>33.656945</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3723,23 +3747,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
+          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14.42809</t>
+          <t>4.75999</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3800,7 +3824,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785629494</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3810,7 +3834,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>23.848083</t>
+          <t>7.771412</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3827,23 +3851,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
+          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>102.61</t>
+          <t>22.01285</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3904,7 +3928,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785629314</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3914,7 +3938,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>172.816842</t>
+          <t>36.012843</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3931,23 +3955,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
+          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>24.94998</t>
+          <t>16.31349</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3978,7 +4002,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4008,7 +4032,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785625675</t>
+          <t>1785629531</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4018,7 +4042,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>33.830481</t>
+          <t>26.908849</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4035,23 +4059,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
+          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>18.03999</t>
+          <t>7.01336</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4059,7 +4087,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4082,7 +4114,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4112,7 +4144,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785623924</t>
+          <t>1785629517</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4122,7 +4154,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>31.579851</t>
+          <t>21.496889</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4139,27 +4171,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
+          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.01902</t>
+          <t>18.47618</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4167,11 +4195,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4194,7 +4218,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4224,7 +4248,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785622155</t>
+          <t>1785629509</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4234,7 +4258,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.30047</t>
+          <t>30.476173</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4251,23 +4275,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
+          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.76998</t>
+          <t>7.01963</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4275,7 +4303,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4298,7 +4330,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4328,7 +4360,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785622131</t>
+          <t>1785629505</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4338,7 +4370,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>32.013441</t>
+          <t>21.516107</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4355,23 +4387,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
+          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>14.42809</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4432,7 +4464,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785618894</t>
+          <t>1785629494</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4442,7 +4474,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>8.595186</t>
+          <t>23.848083</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4459,28 +4491,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>102.61</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4491,27 +4523,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4536,17 +4568,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785629314</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>172.816842</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4563,7 +4595,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4574,12 +4606,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4595,27 +4627,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4640,17 +4672,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4667,27 +4699,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4695,11 +4723,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tecnico U.</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4707,27 +4731,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4752,17 +4776,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4779,7 +4803,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4787,15 +4811,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4803,7 +4831,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4811,27 +4843,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4856,17 +4888,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4883,7 +4915,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4891,19 +4923,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4911,11 +4939,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4923,27 +4947,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4968,17 +4992,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4995,7 +5019,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5003,19 +5027,15 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5023,11 +5043,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5035,27 +5051,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5080,17 +5096,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5107,39 +5123,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5162,7 +5170,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5192,7 +5200,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5202,7 +5210,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5219,7 +5227,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5230,17 +5238,17 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5251,27 +5259,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5296,17 +5304,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5323,12 +5331,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5338,22 +5346,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador -1</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5378,7 +5386,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5408,7 +5416,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5418,7 +5426,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5435,7 +5443,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5443,59 +5451,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5520,17 +5520,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5547,12 +5547,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5562,52 +5562,52 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5659,12 +5659,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5674,52 +5674,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5744,17 +5744,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5771,31 +5771,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5818,7 +5826,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5848,7 +5856,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5858,7 +5866,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5875,28 +5883,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5907,27 +5915,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5952,17 +5960,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5979,59 +5987,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6056,17 +6072,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6083,31 +6099,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6115,27 +6139,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6160,17 +6184,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6187,7 +6211,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6195,23 +6219,31 @@
           <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6219,27 +6251,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6264,17 +6296,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6291,31 +6323,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6323,27 +6363,27 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6368,17 +6408,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6395,7 +6435,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6406,17 +6446,17 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6442,7 +6482,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6472,7 +6512,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6482,7 +6522,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6499,7 +6539,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6510,17 +6550,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6546,7 +6586,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6576,7 +6616,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6586,7 +6626,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6603,28 +6643,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6635,27 +6675,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6680,17 +6720,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6707,7 +6747,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6718,17 +6758,17 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6754,7 +6794,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6784,7 +6824,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6794,7 +6834,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6811,7 +6851,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6822,17 +6862,17 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6858,7 +6898,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6888,7 +6928,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6898,7 +6938,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6915,23 +6955,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6992,7 +7032,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7002,7 +7042,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7019,23 +7059,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7096,7 +7136,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7106,7 +7146,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7123,39 +7163,31 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7178,7 +7210,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7208,7 +7240,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7218,7 +7250,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7235,39 +7267,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7275,27 +7299,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7320,17 +7344,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7347,28 +7371,28 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -7379,27 +7403,27 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -7424,17 +7448,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7451,28 +7475,28 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -7483,27 +7507,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7528,17 +7552,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7555,7 +7579,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7566,17 +7590,17 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -7587,27 +7611,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7632,17 +7656,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7659,7 +7683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7667,31 +7691,23 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7699,27 +7715,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7744,17 +7760,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7771,7 +7787,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7786,22 +7802,22 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7811,27 +7827,27 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -7856,17 +7872,17 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7883,12 +7899,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -7898,29 +7914,29 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>Libertad FC vs Orense Sporting Club</t>
@@ -7938,7 +7954,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7968,7 +7984,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7978,7 +7994,7 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -7995,28 +8011,28 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8027,27 +8043,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8072,17 +8088,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8099,28 +8115,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8131,27 +8147,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8176,17 +8192,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8203,28 +8219,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8235,27 +8251,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8280,17 +8296,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8307,23 +8323,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -8331,7 +8351,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8339,27 +8363,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8384,17 +8408,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8411,31 +8435,39 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8443,27 +8475,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8488,17 +8520,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8515,31 +8547,39 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8547,27 +8587,27 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8592,17 +8632,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8619,7 +8659,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8630,12 +8670,12 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -8696,7 +8736,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8706,7 +8746,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8723,23 +8763,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -8800,7 +8840,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8810,7 +8850,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8827,28 +8867,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0.44982</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8859,27 +8899,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8904,17 +8944,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785459886</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>0.6426</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8931,28 +8971,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>463.04</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -8963,27 +9003,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9008,17 +9048,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785459772</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>712.369231</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9035,23 +9075,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.4363</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -9112,7 +9152,7 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459616</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -9122,7 +9162,7 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>22.555874</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9139,23 +9179,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.435</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -9216,7 +9256,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785459612</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9226,7 +9266,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>45.977011</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9243,23 +9283,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>0.6173</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -9275,27 +9315,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9320,17 +9360,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785459609</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>1.510214</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9347,67 +9387,59 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9432,17 +9464,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785459608</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>112.676056</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9459,39 +9491,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.355</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9499,27 +9523,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9544,17 +9568,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785459600</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>281.690141</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9571,110 +9595,750 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B93" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="T93" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="U93" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr">
+      <c r="V93" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/LigaPro/trades.xlsx
+++ b/data/sxbet/ligas/LigaPro/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x8d2c872c09665cf9cf57507cd03dbbbaf226430f2b1442f9c0bb35deb32aa9ff</t>
+          <t>0xc8bad4f1c222942281d79d887f1ea37e77792f9deb5a1fd9497445fbf8bb8149</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.00062</t>
+          <t>4.67488</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.115</t>
+          <t>1.1863</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (4.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Over 4.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
+          <t>0x50e7fabe73eb610eff694b33295657e56e987db73da49e166d4509c0e601a70d</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19614996</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1785681442</t>
+          <t>1785693305</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1785702600</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>8.701043</t>
+          <t>25.100027</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x6df2851dc28953254a2c8d565a7c08bfd0aaec8318f215c23034e37e288e72aa</t>
+          <t>0xba15803ba72bc44a3a0449a31b52e90bc0a1a352c5927d0cd063931f073749cb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9.554</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.1162</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
+          <t>0xa19ec2b2dfb7b5d3d8a4033f96ebe6481a75f9e3699ed0307c8c036999553cf8</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19614996</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1785681442</t>
+          <t>1785693293</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1785702600</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>34.408602</t>
+          <t>27.297143</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x5754a527c5d40772803bfe08111607b869805453b6d724e4bed89cc5247bd2ad</t>
+          <t>0x518432106fc99636da1d7565b9d79261a1fbf2a50a51a545ad0925b0ef928131</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1125</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1785681235</t>
+          <t>1785692738</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>35.555556</t>
+          <t>8.421053</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x1655d0bff2fd6ee42ddf227545e1a447e622f1ae7851bd36a654f498c9012b54</t>
+          <t>0xbdd60bea64338a7ba28784dbc07681b1770a7d3c5df2d6ae8790b10072f88831</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -875,15 +875,19 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.365</t>
+          <t>1.1187</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -891,7 +895,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -914,7 +922,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -944,7 +952,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1785681139</t>
+          <t>1785691838</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -954,7 +962,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.739726</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,27 +979,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x7118126433717b97d7c36bce57f6385f22f7e374269ac7ca377698d845607115</t>
+          <t>0xddefb7e6afd3c0b8bf2f87ef4f400e0346b35fbce4d2c70996584f1d9a551cf0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>22.77998</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -999,11 +1003,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Independiente del Valle</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Independiente del Valle vs Deportivo Cuenca</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Independiente del Valle</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xf87a3f407757b2ab8e98e67ca4abde0801cbe039cf02f0e2970781f2ca6d2e06</t>
+          <t>0x7d6b2263ce7a3fdfb15bb606245d8b172f0dd51855fafe18054230a68e2e6e8c</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19613834</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1785679495</t>
+          <t>1785691323</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1785693600</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13.157882</t>
+          <t>33.37726</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,39 +1083,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4a6e59d1e415c1dc3913e9219fe2de6baa033f6752aea7f413784c5603109421</t>
+          <t>0x71d5be9f95e59ca8ff946408f2e89f42c0c68825d6cdd95e751ffb934e081b35</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>100.45</t>
+          <t>23.36996</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5075</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Independiente del Valle -1.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1138,7 +1130,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xd1235982bd1809325631bb681de4216922f18a31740b3db578a0a014c1041b71</t>
+          <t>0xdce8f4b7ec9490c1e5b0af393612db9b88c1c0c27eca383f079b22e358b49d93</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1168,7 +1160,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1785678266</t>
+          <t>1785690442</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1178,7 +1170,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>197.931034</t>
+          <t>25.40213</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,12 +1187,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x214f483a273996aa10b912ab8fa07a65283ddd1ef8e14f95c317edc7d6c36ee2</t>
+          <t>0xbe8c993a9ccd2ce30d37f0e560ec160e3788479591fcdc4c3db4d3cc77eb3247</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1210,22 +1202,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>3.60734</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.3137</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0xa19ec2b2dfb7b5d3d8a4033f96ebe6481a75f9e3699ed0307c8c036999553cf8</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1785660120</t>
+          <t>1785690285</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7.776892</t>
+          <t>10.343627</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,12 +1299,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x70ebb7c96f6896fbf14049a85100131a7e0367db64c5d8b3c6e7f9c4f0aecbd0</t>
+          <t>0x880933f90c0f340862854a21286f0aeef2bfacde4e7a92b0678b12336b984d07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1322,22 +1314,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>16.46309</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.3137</t>
+          <t>1.3487</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1347,27 +1339,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
+          <t>0xa19ec2b2dfb7b5d3d8a4033f96ebe6481a75f9e3699ed0307c8c036999553cf8</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1392,17 +1384,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1785659777</t>
+          <t>1785690285</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11.314741</t>
+          <t>47.205993</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1419,7 +1411,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
+          <t>0xca5ca80cc956cfb4e083ad918b0d0249d9f4ea84ef60091d9371f553a56974a9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1434,12 +1426,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1504,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1785643501</t>
+          <t>1785690268</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1514,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>13.34413</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1531,7 +1523,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
+          <t>0x29ef8a18d72ac364813d93488229efd8cd88ea0321a5877d32fd8a9bc90518b3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1546,12 +1538,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.01884</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1616,7 +1608,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1785643470</t>
+          <t>1785689361</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1626,7 +1618,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>32.318839</t>
+          <t>25.910931</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1643,12 +1635,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
+          <t>0xc15366b89fd8031a5b9c0ca352d3ff7da2ac0ff0302c9551c01247c9374cfa2e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1658,22 +1650,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.6425</t>
+          <t>1.3438</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Over 3.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1683,27 +1675,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Club Social Y Deportivo Macara</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
+          <t>0xa19ec2b2dfb7b5d3d8a4033f96ebe6481a75f9e3699ed0307c8c036999553cf8</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19614996</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1728,17 +1720,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1785643468</t>
+          <t>1785688781</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1785702600</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>26.085603</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1755,31 +1747,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
+          <t>0xd3c6ed39fdada59668f702d949df783b56463f7e4970529d992a65742c4998d3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x3b2B3900de9f93d1a397Efd858D1035643D15F96</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.25205</t>
+          <t>487.9086</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.9525</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -1787,27 +1787,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xc9955b578d39f9f0dbbfc422ce82181967491807dd8dec555e467982b343f230</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1785631027</t>
+          <t>1785688303</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3.144223</t>
+          <t>512.24</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1859,12 +1859,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
+          <t>0x6e456721822cec39625578ccfe0274161675df8b0b69d580a42e36a5a2c5993d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>1.1687</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1899,27 +1899,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0x99bafd078f9b79677bcff2b1dc12517292db8af37faabdc8222e9a6fb42dae6e</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1785631010</t>
+          <t>1785688167</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>35.392405</t>
+          <t>21.866667</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
+          <t>0x8d2c872c09665cf9cf57507cd03dbbbaf226430f2b1442f9c0bb35deb32aa9ff</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1.00062</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.3787</t>
+          <t>1.115</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2056,17 +2056,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1785630610</t>
+          <t>1785681442</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>31.049505</t>
+          <t>8.701043</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2083,23 +2083,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
+          <t>0x6df2851dc28953254a2c8d565a7c08bfd0aaec8318f215c23034e37e288e72aa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6562</t>
+          <t>1.1162</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2107,7 +2111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2115,27 +2123,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2160,17 +2168,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1785630479</t>
+          <t>1785681442</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>34.408602</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2187,23 +2195,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
+          <t>0x5754a527c5d40772803bfe08111607b869805453b6d724e4bed89cc5247bd2ad</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.24054</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6362</t>
+          <t>1.1125</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2211,7 +2223,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Guayaquil City</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2219,27 +2235,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xbca5d14d29179e53bba4849b1acbd1927007a962ff135830ed78ba22af675632</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2264,17 +2280,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1785629993</t>
+          <t>1785681235</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>30.240534</t>
+          <t>35.555556</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2291,23 +2307,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
+          <t>0x1655d0bff2fd6ee42ddf227545e1a447e622f1ae7851bd36a654f498c9012b54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.93057</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.365</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2323,27 +2339,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2368,17 +2384,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1785629981</t>
+          <t>1785681139</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>29.811921</t>
+          <t>2.739726</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2395,23 +2411,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
+          <t>0x7118126433717b97d7c36bce57f6385f22f7e374269ac7ca377698d845607115</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.20642</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2419,7 +2439,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2427,27 +2451,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xf87a3f407757b2ab8e98e67ca4abde0801cbe039cf02f0e2970781f2ca6d2e06</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2472,17 +2496,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1785629980</t>
+          <t>1785679495</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.325071</t>
+          <t>13.157882</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2499,31 +2523,39 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
+          <t>0x4a6e59d1e415c1dc3913e9219fe2de6baa033f6752aea7f413784c5603109421</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>0x12e3C74BC44f9C2C1f9215a84C3862510219Dd10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>20.8767</t>
+          <t>100.45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>1.5075</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Independiente del Valle -1.5</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2531,27 +2563,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Independiente del Valle vs Deportivo Cuenca</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Independiente del Valle</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xd1235982bd1809325631bb681de4216922f18a31740b3db578a0a014c1041b71</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19613834</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2576,17 +2608,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1785629947</t>
+          <t>1785678266</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785693600</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>32.876693</t>
+          <t>197.931034</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2603,23 +2635,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
+          <t>0x214f483a273996aa10b912ab8fa07a65283ddd1ef8e14f95c317edc7d6c36ee2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.74447</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2627,7 +2663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2635,27 +2675,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2680,17 +2720,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1785629890</t>
+          <t>1785660120</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>2.808</t>
+          <t>7.776892</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2707,23 +2747,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
+          <t>0x70ebb7c96f6896fbf14049a85100131a7e0367db64c5d8b3c6e7f9c4f0aecbd0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.68316</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.3137</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2731,7 +2775,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2739,27 +2787,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2784,17 +2832,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1785629849</t>
+          <t>1785659777</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>31.683155</t>
+          <t>11.314741</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2811,23 +2859,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
+          <t>0x3a8024ba26dbbfd4c6646fe78017da7bb31a944e78d3d4df35437870d2317aa9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22.72134</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2835,7 +2887,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2843,27 +2899,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2888,17 +2944,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1785629842</t>
+          <t>1785643501</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>36.647323</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2915,23 +2971,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
+          <t>0x2d6708dc3366665abc8912fb0761bbc586fcb67ad546920c428571cf9260f715</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.12077</t>
+          <t>10.01884</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2939,7 +2999,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -2947,27 +3011,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x9634db292e5433bc5cc150ae505e21b8f9ac5056c724feb946c7b3247ab527bc</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2992,17 +3056,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1785629837</t>
+          <t>1785643470</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.19479</t>
+          <t>32.318839</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3019,23 +3083,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
+          <t>0x9961578445f7270bd8572075b9b52ac082f559cd83aca7942b8fb77dd48d18b5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22.96368</t>
+          <t>16.76</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6212</t>
+          <t>1.6425</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3043,7 +3111,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Club Social Y Deportivo Macara</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3051,27 +3123,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Club Social Y Deportivo Macara vs Guayaquil City</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Club Social Y Deportivo Macara</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x7f936aee6dfeb8b1fd75b78a8228cdd95d0ec416747473ad33c316097bcb55b0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19614996</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3096,17 +3168,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785643468</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785702600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.96367</t>
+          <t>26.085603</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3123,23 +3195,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
+          <t>0x05af888f68fc1795902f5d642bccd708749870bb9ec38557877f0bc823ebc9d3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>21.21051</t>
+          <t>2.25205</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3170,7 +3242,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3200,7 +3272,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1785629821</t>
+          <t>1785631027</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3210,7 +3282,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>34.2105</t>
+          <t>3.144223</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3227,7 +3299,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
+          <t>0xa1bd132a0eedae9be9b499c6038d7567892bf90240e6703cc41b1f9f574f6833</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3235,15 +3307,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>21.09838</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.395</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3251,7 +3327,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3274,7 +3354,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3304,7 +3384,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1785629804</t>
+          <t>1785631010</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3314,7 +3394,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>34.029645</t>
+          <t>35.392405</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3331,23 +3411,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
+          <t>0x4aa39595be71d5678398e24e9cd98706a828d42583a3f2954f22d6697789ad7a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.11216</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.3787</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3355,7 +3439,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -3378,7 +3466,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3408,7 +3496,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1785629795</t>
+          <t>1785630610</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3418,7 +3506,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>0.180903</t>
+          <t>31.049505</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3435,7 +3523,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
+          <t>0x9562bd2749636492679e4613e468f06a8ed9627721d332e6c53699313e18d238</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3446,12 +3534,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22.7213</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.6187</t>
+          <t>1.6562</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3512,7 +3600,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1785629790</t>
+          <t>1785630479</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3522,7 +3610,7 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>36.721293</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3539,7 +3627,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
+          <t>0xa250e093d7527f93ecdc5feab50c90040ceadb4375fad759a0c4c20220d9e598</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3550,12 +3638,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22.6013</t>
+          <t>19.24054</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.6175</t>
+          <t>1.6362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3616,7 +3704,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1785629787</t>
+          <t>1785629993</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3626,7 +3714,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>36.601296</t>
+          <t>30.240534</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3643,7 +3731,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
+          <t>0x8d8188c34faba5624b7974be9874164c534ad289782af59223e9349b41cb3bf3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3654,12 +3742,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20.65695</t>
+          <t>18.93057</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.6138</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3720,7 +3808,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1785629635</t>
+          <t>1785629981</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3730,7 +3818,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>33.656945</t>
+          <t>29.811921</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3747,23 +3835,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
+          <t>0xf2fc80082a439acb920fb97a14e23a1fbe0d7c46c78f5b4d1b5bfbbab182bf4e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.75999</t>
+          <t>0.20642</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.6125</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3824,7 +3912,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629980</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3834,7 +3922,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>7.771412</t>
+          <t>0.325071</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3851,7 +3939,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
+          <t>0x382bd2b8a10cf7aced069d8f05c9b8ceaac969ce62d3cbd1bb98f885e8da6fc8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3862,12 +3950,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22.01285</t>
+          <t>20.8767</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.6113</t>
+          <t>1.635</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3928,7 +4016,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1785629582</t>
+          <t>1785629947</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3938,7 +4026,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>36.012843</t>
+          <t>32.876693</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3955,7 +4043,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
+          <t>0xa445b75847d6fbd219d27bf44ad51fba5f87af913b2f266b8c130ed91a40ef75</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3966,12 +4054,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16.31349</t>
+          <t>1.74447</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4032,7 +4120,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1785629531</t>
+          <t>1785629890</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4042,7 +4130,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>26.908849</t>
+          <t>2.808</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4059,7 +4147,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
+          <t>0x948e01b2115d587e3f32db0bc091ff9ff22511fae3f45b6795917a0de6093199</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4067,19 +4155,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.01336</t>
+          <t>19.68316</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4087,11 +4171,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4114,7 +4194,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4144,7 +4224,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1785629517</t>
+          <t>1785629849</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4154,7 +4234,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>21.496889</t>
+          <t>31.683155</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4171,7 +4251,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
+          <t>0x1c584233c6732779d4f8caf8b435febfe0caf7bcecd48bb781c2c3be12628378</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4182,12 +4262,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18.47618</t>
+          <t>22.72134</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.6062</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4248,7 +4328,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1785629509</t>
+          <t>1785629842</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4258,7 +4338,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>30.476173</t>
+          <t>36.647323</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4275,7 +4355,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
+          <t>0x0c6c5b313379aa0bcacf0a469ff4b2e5cbf8aad868730e56b33ccbac160bea2a</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4283,19 +4363,15 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>7.01963</t>
+          <t>0.12077</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.3262</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4303,11 +4379,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4330,7 +4402,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4360,7 +4432,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1785629505</t>
+          <t>1785629837</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4370,7 +4442,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>21.516107</t>
+          <t>0.19479</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4387,7 +4459,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
+          <t>0x8209dd034dfd1b515af860a8201e5c674cafbf036312a741391d725faa2fd388</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4398,12 +4470,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>14.42809</t>
+          <t>22.96368</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.605</t>
+          <t>1.6212</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4464,7 +4536,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1785629494</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4474,7 +4546,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>23.848083</t>
+          <t>36.96367</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4491,23 +4563,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
+          <t>0x6418c1fe648ecc9bd0adbb4300bd224f7b15bb2da26376203606b62785806d5d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>102.61</t>
+          <t>21.21051</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5938</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4568,7 +4640,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1785629314</t>
+          <t>1785629821</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4578,7 +4650,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>172.816842</t>
+          <t>34.2105</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4595,23 +4667,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
+          <t>0x1170e7020a69e2143370a78010228c346693b0867ed59589484e304cfce5e69f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>24.94998</t>
+          <t>21.09838</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.7375</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4642,7 +4714,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4672,7 +4744,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1785625675</t>
+          <t>1785629804</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4682,7 +4754,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>33.830481</t>
+          <t>34.029645</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4699,23 +4771,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
+          <t>0x73725490fd950d95526008d1aa29c0e25cbf606d914a6d6b8b3df3c007d75ff1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>18.03999</t>
+          <t>0.11216</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4776,7 +4848,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1785623924</t>
+          <t>1785629795</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4786,7 +4858,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>31.579851</t>
+          <t>0.180903</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4803,27 +4875,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
+          <t>0xb5aa8b92d928718872ad09bb8bf741aa67b8fae2e2130baa3517ab4911684422</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.01902</t>
+          <t>22.7213</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.3088</t>
+          <t>1.6187</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4831,11 +4899,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -4858,7 +4922,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4888,7 +4952,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1785622155</t>
+          <t>1785629790</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4898,7 +4962,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>3.30047</t>
+          <t>36.721293</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4915,23 +4979,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
+          <t>0xf3a036488603847de9fb6c7e209f6f388ecf5ac0b1a6eef21823674dae91fdd0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>23.76998</t>
+          <t>22.6013</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7425</t>
+          <t>1.6175</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4962,7 +5026,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4992,7 +5056,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1785622131</t>
+          <t>1785629787</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -5002,7 +5066,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>32.013441</t>
+          <t>36.601296</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5019,23 +5083,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
+          <t>0xe5126f5af60de7c3562604a2b2667f2355dc57fbfbdad4f61069b027608adb8b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>20.65695</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.6138</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5096,7 +5160,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1785618894</t>
+          <t>1785629635</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5106,7 +5170,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>8.595186</t>
+          <t>33.656945</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5123,28 +5187,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
+          <t>0xfca71c16b3e51ba69a44b0ec8b3e66f149ab4ea858b28cfcf25c5cc9a40fd57f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>4.75999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.1525</t>
+          <t>1.6125</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5155,27 +5219,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5200,17 +5264,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1785617083</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>11.344262</t>
+          <t>7.771412</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5227,23 +5291,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
+          <t>0x90279b53fdd270a1f3173e919bdf33b4a8d9892b9b21e3ed6b1ee52333687a13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>22.01285</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.875</t>
+          <t>1.6113</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5259,27 +5323,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5304,17 +5368,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1785616859</t>
+          <t>1785629582</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>36.012843</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5331,27 +5395,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
+          <t>0x0180d2224247ebd0601419a77cedb36ccf0e9b3ca6ec19d2ca72b28c977bc035</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16.31349</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.1287</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5359,11 +5419,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Tecnico U.</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5371,27 +5427,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5416,17 +5472,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1785616850</t>
+          <t>1785629531</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>108.737864</t>
+          <t>26.908849</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5443,23 +5499,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
+          <t>0xd02f1deb00e6a634d49c63266a829b9a1974767eb79c2343ff72cc0b345a9681</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>38.02995</t>
+          <t>7.01336</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.8588</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5467,7 +5527,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5475,27 +5539,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5520,17 +5584,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1785616283</t>
+          <t>1785629517</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>44.28524</t>
+          <t>21.496889</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5547,27 +5611,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
+          <t>0x8d8121881240252b1a15197d3a97222ea9bbc981e63ccc9e7c58cc05af4d8c1d</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8.00529</t>
+          <t>18.47618</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.6062</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5575,11 +5635,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5587,27 +5643,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5632,17 +5688,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785629509</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>34.24723</t>
+          <t>30.476173</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5659,12 +5715,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
+          <t>0xa5b89af90e17fc39c31420ce9d43a86a37c6ef9e6d294fd256445b3fb0e81ae1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5674,12 +5730,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.01963</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.2325</t>
+          <t>1.3262</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5699,27 +5755,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5744,17 +5800,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1785615140</t>
+          <t>1785629505</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>34.451613</t>
+          <t>21.516107</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5771,27 +5827,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
+          <t>0x96a2d9730abc27ed734ebb0c0096d7ebbf4514521dc9c87c7a525a378d179c09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14.42809</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.2338</t>
+          <t>1.605</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5799,11 +5851,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -5811,27 +5859,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5856,17 +5904,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1785615126</t>
+          <t>1785629494</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>4.278075</t>
+          <t>23.848083</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5883,7 +5931,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
+          <t>0x8416ee2e3d811334c49939caedc86164b7f32ea6843b956e36bcd389bd92fb46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5894,17 +5942,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>102.61</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.8325</t>
+          <t>1.5938</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5915,27 +5963,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5960,17 +6008,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1785613773</t>
+          <t>1785629314</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1.201201</t>
+          <t>172.816842</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5987,39 +6035,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
+          <t>0xe7e31dcf4e7091b0016161d9c81726ff15809ad88271acf1824432a40d628393</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24.94998</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.5025</t>
+          <t>1.7375</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Universidad Catolica del Ecuador -1</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6027,27 +6067,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6072,17 +6112,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1785608052</t>
+          <t>1785625675</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>19.900498</t>
+          <t>33.830481</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6099,7 +6139,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
+          <t>0x12b6130505cc8a8edf5b6b4633ba05d9b11cdfa9fac4d8bee6b88abd448c05b2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6107,59 +6147,51 @@
           <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.24999</t>
+          <t>18.03999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6184,17 +6216,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1785586109</t>
+          <t>1785623924</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>2.48137</t>
+          <t>31.579851</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6211,12 +6243,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
+          <t>0xcc3b3eaa312e1ba91ace2a7e33152f89d15f90298b8362a11344d1642edf31a5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -6226,52 +6258,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>115.96999</t>
+          <t>1.01902</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.3088</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xa4378818fe199cf14694deadcf64f72a55b11388e479f6e1fe65c1cd5122ed90</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6296,17 +6328,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1785581613</t>
+          <t>1785622155</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>233.692675</t>
+          <t>3.30047</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6323,67 +6355,59 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
+          <t>0x7db9d72fe05e9c0b7cafae80909132292491f895d8118cd2683b7b765f885fc6</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>23.76998</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4963</t>
+          <t>1.7425</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Manta FC 0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
+          <t>0xbef81e804b45a008094d3ed28e67d3330de2ca8be595e69a04b9ef716d1b1ec9</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6408,17 +6432,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1785579320</t>
+          <t>1785622131</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>233.692695</t>
+          <t>32.013441</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6435,28 +6459,28 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
+          <t>0x39eb8621b888d9150a0d16c36b67e7d90727962020bed6edde941fa0cb4d01a1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -6467,27 +6491,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6512,17 +6536,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785618894</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>8.595186</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6539,28 +6563,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
+          <t>0x1c5449fdfedcee8971c0c384741afccf1819625941cea175c42c57045be09079</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0x1111084DE52322898FE58e14BCC4824Bf3fEbcfa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -6586,7 +6610,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xc4044a0346c09a988a8646f1c19fcf4f0aebf02dd86358ff869417e13a149799</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6616,7 +6640,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1785559247</t>
+          <t>1785617083</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6626,7 +6650,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>29.554023</t>
+          <t>11.344262</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6643,28 +6667,28 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
+          <t>0x49fe40db9721a6aaa44c12cdaa59de055cc21b9adc2a34ca866505256192b968</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5238</t>
+          <t>1.875</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -6675,27 +6699,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6720,17 +6744,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1785559217</t>
+          <t>1785616859</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1.909308</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6747,31 +6771,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
+          <t>0x4d5eee136de8446546eda81cbb34b3151a02e3a65539b580d186d7b15e7a047c</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x68E1818FF20BBe84F9be9E0A4A395FB11079Bd35</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.1287</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tecnico U.</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -6794,7 +6826,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6824,7 +6856,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785616850</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6834,7 +6866,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>108.737864</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6851,28 +6883,28 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
+          <t>0xd36df2627cc88fab7fdc1af73b8bcb3c0bf72929e79cf6bd4528a73bb336310c</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>38.02995</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.5425</t>
+          <t>1.8588</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6898,7 +6930,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x31555f5a7bf5aa548ff66c4f2796f1137f0693f711b4b80344d2077fd6766592</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6928,7 +6960,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1785559203</t>
+          <t>1785616283</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6938,7 +6970,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>29.474654</t>
+          <t>44.28524</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6955,31 +6987,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
+          <t>0x5003aa71c29014639de94cd36c0d56636b10b1886f45c744d5d916eb60a6228c</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>8.00529</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7002,7 +7042,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -7032,7 +7072,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1785559136</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -7042,7 +7082,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>34.24723</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7059,31 +7099,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
+          <t>0x47ab07234e0925e967962637a863ed524a79d48b9d461f04f5d7dcb51a9077bd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.2325</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7106,7 +7154,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -7136,7 +7184,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>1785559135</t>
+          <t>1785615140</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -7146,7 +7194,7 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>29.314815</t>
+          <t>34.451613</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -7163,31 +7211,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
+          <t>0x4a0fce837f4b39328cc4cb76d4060e94a4597f4078a1ad0dff75a038c5d092c3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.2338</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7210,7 +7266,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -7240,7 +7296,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785615126</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7250,7 +7306,7 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>4.278075</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7267,28 +7323,28 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
+          <t>0xe7448cde3292b98680d8d685555b200090ccc908e6930965d17be8e6401d5629</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.8325</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
+          <t>Under/Over (5)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -7299,27 +7355,27 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xb4df2c601601b81281545002a7ee9a847a424801fa9f9ea09b68e930c647c2b2</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -7344,17 +7400,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>1785559114</t>
+          <t>1785613773</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>1.201201</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7371,23 +7427,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
+          <t>0xcac4d184a3b30b230068ae9c913c5c20aa85bbc70c10395795d8dd47887baf38</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
+          <t>0xf4a8B27C9a13e298D65b5Cc072d252816B799C81</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5025</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7395,7 +7455,11 @@
           <t>Asian Handicap (-1)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Universidad Catolica del Ecuador -1</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7448,7 +7512,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785608052</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7458,7 +7522,7 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>19.900498</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7475,31 +7539,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
+          <t>0xd0a1fa503ade1da26d628202443f8fbf442918a501c47262abc2f7e2c7aedf1c</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>1.24999</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7507,27 +7579,27 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -7552,17 +7624,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>1785559105</t>
+          <t>1785586109</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>29.153488</t>
+          <t>2.48137</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
@@ -7579,31 +7651,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
+          <t>0x29e965d551245d9018463e50f9075f83b10aff02f39db068d1c37a5ff4723160</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>115.96999</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1.5)</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7611,27 +7691,27 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -7656,17 +7736,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>1785557644</t>
+          <t>1785581613</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>233.692675</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7683,31 +7763,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
+          <t>0x36bdf43768d097bea2b6b7cf8c8eb40a364f6be26bcc2bdbc34a4358bd15f24a</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>0x358078dD5Ee4d532029b3cD743Bba2B6EFF8c6CA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>173.57</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>1.5375</t>
+          <t>1.4963</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Asian Handicap (-1)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Manta FC 0</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7715,27 +7803,27 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Universidad Catolica del Ecuador</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Tecnico U.</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
+          <t>0xe3889fc065cfbda24effd8d65ae7dcf33bf6217b69edbfc67fe5a5410d79353b</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>L19606829</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -7760,17 +7848,17 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>1785557643</t>
+          <t>1785579320</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>1785619800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>322.92093</t>
+          <t>233.692695</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
@@ -7787,39 +7875,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
+          <t>0xb2e4c02e28211933f6b928f86cac2342a44028e4a06834899e2493f826b3d18d</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.4062</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Under/Over (3)</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Over 3.0</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7842,7 +7922,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7872,7 +7952,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>1785540081</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7882,7 +7962,7 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
@@ -7899,39 +7979,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
+          <t>0x8684b80e20e5839ef45c647ced9fdb6ad817bd8ed8ee9f052ed9fb1e53314f20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.3313</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Libertad FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -7939,27 +8011,27 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -7984,17 +8056,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>1785524760</t>
+          <t>1785559247</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>3.018868</t>
+          <t>29.554023</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
@@ -8011,12 +8083,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
+          <t>0x3d067f145172c50e59ca0b4e380527c6465e9e7bced485ec545a5a801da4f192</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x5D69C3af95Ff47088b415B25F41b1fFDc8571063</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -8027,12 +8099,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1.5913</t>
+          <t>1.5238</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -8043,27 +8115,27 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Emelec vs Aucas</t>
+          <t>Manta FC vs Mushuc Runa</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Emelec</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Aucas</t>
+          <t>Mushuc Runa</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>L19607503</t>
+          <t>L19605615</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -8088,17 +8160,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>1785513340</t>
+          <t>1785559217</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>1785628800</t>
+          <t>1785610800</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1.691332</t>
+          <t>1.909308</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -8115,28 +8187,28 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
+          <t>0xe49aa1402b07e6a57788597efc22d36ee0bc2a44d12f4a67ccad485901181f5c</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>1.6825</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -8147,27 +8219,27 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -8192,17 +8264,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>1785513160</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1.465201</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8219,28 +8291,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
+          <t>0x112a021845fe9bf95e367a0f700b597eb7a83a0ba4ffbe214ad8927ed4f5ca3b</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>18.41999</t>
+          <t>15.99</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1.5537</t>
+          <t>1.5425</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LigaPro</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -8251,27 +8323,27 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -8296,17 +8368,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>1785497374</t>
+          <t>1785559203</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>33.26409</t>
+          <t>29.474654</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -8323,39 +8395,31 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
+          <t>0xcd930a180859d9aa8e9ec5063039c25a51d1b84f426ce098fab2b826be43c14e</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
+          <t>15.83</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>1.3738</t>
-        </is>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8363,27 +8427,27 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -8408,17 +8472,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>1785497256</t>
+          <t>1785559136</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>4.120401</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -8435,39 +8499,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
+          <t>0x55c713e486fd070fd153fe7b8a4740d30756c92c24199ced6ae9a4fb21d66032</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>15.65</t>
+          <t>15.83</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>1.3738</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Orense Sporting Club</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -8475,27 +8531,27 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -8520,17 +8576,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>1785497255</t>
+          <t>1785559135</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>41.87291</t>
+          <t>29.314815</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8547,67 +8603,59 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
+          <t>0xa1be8be545a12de4b1d2eb30fc36822fcea98c5b6477da0386665686d8546491</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>1.5038</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>Asian Handicap (-1.5)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Libertad FC 0</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Libertad FC vs Orense Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Orense Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>L19614758</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -8632,17 +8680,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>1785487800</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>1785542400</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>7.543424</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -8659,28 +8707,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
+          <t>0x689ddef40b716c0d441f47a869b282dbf7e1f244a3db28a2be41cb4824098592</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -8691,27 +8739,27 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -8736,17 +8784,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>1785460511</t>
+          <t>1785559114</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>27.210884</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -8763,28 +8811,28 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
+          <t>0xffe8d26c7257da8b1458a45b7ac21e2ee10747a7829189f377bdbdd795abc7f3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>1.3675</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -8795,27 +8843,27 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -8840,17 +8888,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>1785460290</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>26.122449</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -8867,28 +8915,28 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+          <t>0x1979af5cdf97b6ea5b2ba5732ba661a3af4f1eb07d15243486541a2391455fb2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x4c67719710F563c9CE4Df1836c8d643BACc6986a</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0.44982</t>
+          <t>15.67</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -8899,27 +8947,27 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -8944,17 +8992,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>1785459886</t>
+          <t>1785559105</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>0.6426</t>
+          <t>29.153488</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -8971,28 +9019,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+          <t>0xebf29524cca596e42a9c958e8921be8876eeae25d2e79f7280c89fecef315b1e</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>463.04</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-1.5)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -9003,27 +9051,27 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xe4329a308902f0dc55a206367f7da0dd7eca95268d2af0c7d48cb5f71117e8d8</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -9048,17 +9096,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>1785459772</t>
+          <t>1785557644</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>712.369231</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -9075,28 +9123,28 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+          <t>0x27a2ff7d9b798a83f7ef4730f744085ed74d62b54823ad85bbbf1ec8a89aea9f</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>173.57</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1.4363</t>
+          <t>1.5375</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Asian Handicap (-1)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -9107,27 +9155,27 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x23ca4379e0a47d5d152839e779d31257e03c01698f52329f5164b3eb1619224a</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -9152,17 +9200,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>1785459616</t>
+          <t>1785557643</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>22.555874</t>
+          <t>322.92093</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
@@ -9179,31 +9227,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+          <t>0x9879a7b6cfc4fa023c72052a5b9881737a2eec7ddd2bd1d9bfeb15797c9d8925</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>1.435</t>
+          <t>1.4062</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9211,27 +9267,27 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Tecnico U.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0x066dc3fa4a3c8700f5683a34451f545686c5314e17533d096bcb8664c8b07137</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19606829</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -9256,17 +9312,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>1785459612</t>
+          <t>1785540081</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785619800</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>45.977011</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -9283,31 +9339,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+          <t>0x572942571527f4a285d724ce3da87dc60480f515ece4ccc38a99dfb2599b1fb7</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>0.6173</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.3313</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9315,27 +9379,27 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -9360,17 +9424,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>1785459609</t>
+          <t>1785524760</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1.510214</t>
+          <t>3.018868</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -9387,28 +9451,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+          <t>0x3378821d00d0f476caa79caf9d32e8a08b63b698067887429774c9e1ced599de</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -9419,27 +9483,27 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Emelec vs Aucas</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Emelec</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Aucas</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xfb32031071813c746101fb9b0b752f058f1224fcef739c0a06325a255b6fd53e</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19607503</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -9464,17 +9528,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>1785459608</t>
+          <t>1785513340</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785628800</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>112.676056</t>
+          <t>1.691332</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -9491,28 +9555,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+          <t>0x12a039076c870c861492e25d9c04b652c8b4d4361cbc2283125f6def10853274</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.6825</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -9523,27 +9587,27 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xb211cc5404a48394b77e502360583ec16cd625ee74c5e5885308d65ddc497907</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -9568,17 +9632,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>1785459600</t>
+          <t>1785513160</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>281.690141</t>
+          <t>1.465201</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -9595,28 +9659,28 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+          <t>0xa5b3d68b2642f8317db5aa6234979468ffd316702aa575ccca861a5abb45dbfa</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18.41999</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.5537</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>LigaPro</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -9627,27 +9691,27 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xc414d1851d332f14f9b904e5e2f8963b17d626ab4fedbfd1d860c5ca0d8a5c2e</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -9672,17 +9736,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>1785459599</t>
+          <t>1785497374</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>45.070423</t>
+          <t>33.26409</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -9699,31 +9763,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+          <t>0xf869759eb33d130e04144d3df7eb2a15b9e83af58f09e56bef9af7da2e867274</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9731,27 +9803,27 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -9776,17 +9848,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785497256</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>56.338028</t>
+          <t>4.120401</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -9803,31 +9875,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+          <t>0x6bf9bf6d90ab05711b64e3258529a8073c4bb1056bff9906eee709566f785280</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15.65</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1.3738</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9835,27 +9915,27 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Leones Del Norte</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Barcelona Sporting Club</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+          <t>0xd8a8103adc6de6609b86d3c49639d966c7a1b009d923b1c33f1687d853406004</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>L19615984</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -9880,17 +9960,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>1785459589</t>
+          <t>1785497255</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>1785712200</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>22.535211</t>
+          <t>41.87291</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -9907,31 +9987,39 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+          <t>0x91afdb3056b97dc838512da3006edc8d40d795e1cbf61754dd27b42bffbd9db4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>0xFD3a22179CA4104E97c670b834750Bd7Ff310b17</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>133.14</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1.3475</t>
+          <t>1.5038</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Libertad FC 0</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -9939,27 +10027,27 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Libertad FC vs Orense Sporting Club</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Orense Sporting Club</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+          <t>0xf805a6b6914a32854187614782fd2287c1f192abfc5aeb543744efbea5dd36e2</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19614758</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -9984,17 +10072,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>1785459478</t>
+          <t>1785487800</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785542400</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>383.136691</t>
+          <t>7.543424</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -10011,67 +10099,59 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+          <t>0xcdbab7f720ecc2609cc986e33ee19c14fa06efd04db5f8d0ad2191eac40b0fc7</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>250.01</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1.4812</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>LigaPro</t>
-        </is>
-      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -10096,17 +10176,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>1785441463</t>
+          <t>1785460511</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>519.501299</t>
+          <t>27.210884</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -10123,39 +10203,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+          <t>0x8eed2f9e278deaeb4e1628ba136974f1228d0035db9cb9a273c6e2e8572240ac</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x3287C9BCD7D05d027E8398cCAfE385a232D16B2C</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>141.16</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1.3438</t>
+          <t>1.3675</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>LigaPro</t>
@@ -10163,27 +10235,27 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Manta FC vs Mushuc Runa</t>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones Del Norte</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Mushuc Runa</t>
+          <t>Barcelona Sporting Club</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>L19605615</t>
+          <t>L19615984</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -10208,17 +10280,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>1785441440</t>
+          <t>1785460290</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>1785610800</t>
+          <t>1785712200</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>410.647273</t>
+          <t>26.122449</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -10235,110 +10307,1478 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>0x5cef349f9cfb08f0092efea94b1e1eba2316aeb489bcac201bd39d8fcdf537c8</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0.44982</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1785459886</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>0.6426</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>0x4ec9bf0ae9b293566857be0aa3d45d789368888ea7711a80eb74a83b16d81f4e</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0x0fE55cE066A9810115Ea99B11a14e96a4b635810</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>463.04</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>1785459772</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>712.369231</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>0xbd33d07c10885c67a924c31f597f4aa5269e749d7ebe942f21e7126f5b3963fb</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>9.84</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.4363</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>1785459616</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>22.555874</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>0x822816cff19781f933159cdf709b5e367523844ca5b9fd352afa4ced63e4f188</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.435</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>1785459612</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>45.977011</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0x112b0eec53123207d54d485755814cb85c7a0e1221a71fe48e719c11999f226b</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0.6173</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.4087</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>1785459609</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1.510214</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>0x6d2158602245d1bbacc34a6453b10a1fe16d7c6af14c30668a211849eeb8ba5b</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>1785459608</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>112.676056</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0x31f03e88b769cce674016ee1a73349f277ff02ed997281a0fac5b88a4adc21b5</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1785459600</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>281.690141</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0xeaf9f248dc1ebc5d9a1f2fdbcc82110f148761403b799b4f1d66fdcd0611ef42</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0x3509E838511034368Ed1aA44b85Bc5b1af675684</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>1785459599</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>45.070423</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0xe0216d65c84aa6a069cef40fe70d14810fef09d2e27e600aa1801d2b644c168e</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>56.338028</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0x5386cc079cbea6f8024fcb1f4fd8c125fdb9c4d4507d7d72667521bc2234711c</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0xefEd5719272d06dDD2e1e383C3076aa8262a2C55</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.355</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Leones Del Norte vs Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Leones Del Norte</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Barcelona Sporting Club</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0xaa6e0d011cd1f0f90445686073986da2b91bd350bd98d5463185fb2d4823b6c3</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>L19615984</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>1785459589</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>1785712200</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>22.535211</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0x588486ac7bdc3d012f0c913f77b7dabec6ba1e59371770a8a166aede4963f976</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0x24B2465f0c768EdAA0DEBbb7DB5C6345239F7d87</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>133.14</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.3475</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0x28d74792b0065ec6861aca96e85c560a964fd866c6e9a22a3d23b26ddaaee489</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>1785459478</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>383.136691</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0x7309daf787ae3e353d988657b675fea72aff1d7086065c258d3c16a3a73012a8</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>250.01</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.4812</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>0x8eedc564abb7307b4ef89fa66291601295b22578d5296ac8e0af172b47a57d7c</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>1785441463</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>519.501299</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>0x1f7f2d61f5529a2354ab2c3ca0ce271c1931037e2901585e390e07f87e506ee0</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0xF974DAF59EA0cdfBD2125EcBB5BacEBA8F4727dA</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>141.16</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.3438</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>LigaPro</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Manta FC vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0x6bb6296b7aec74167b3bd11b6c86d525a8bef7b59c2155a1e98611017de1a15f</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>L19605615</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>1785441440</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>1785610800</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>410.647273</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>0x6599044f3d4d50487489b07a035618092f1d03440ffd54856dcd903844650bb5</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>0x44a80DC6b2015FBaC7a505fB0D7CCa1FAC58C7Bf</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>1.2575</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Tie</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>LigaPro</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador vs Tecnico U.</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Universidad Catolica del Ecuador</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Tecnico U.</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>0x6f48cb9ab2adc3f80f8a9cce4985a85384a62c4eb9ef39c2fcda8ffbe498fcac</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>L19606829</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
         <is>
           <t>1785344362</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>1785619800</t>
         </is>
       </c>
-      <c r="T93" t="inlineStr">
+      <c r="T106" t="inlineStr">
         <is>
           <t>3.883495</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="U106" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="V106" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
